--- a/resources/templates/original_income_template.xlsx
+++ b/resources/templates/original_income_template.xlsx
@@ -89,10 +89,10 @@
     <t>REMARK2</t>
   </si>
   <si>
-    <t>aliigners upper and lower and nighgaurd</t>
+    <t>sample treatment description</t>
   </si>
   <si>
-    <t>tranfer to dr wael</t>
+    <t>sample transfer note</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -107,43 +107,43 @@
     <t>Item</t>
   </si>
   <si>
-    <t>MIDDLE EAST LAB</t>
+    <t>Lab Vendor 1</t>
   </si>
   <si>
-    <t>Qualia</t>
+    <t>Lab Vendor 2</t>
   </si>
   <si>
-    <t>AL MAHA</t>
+    <t>Lab Vendor 3</t>
   </si>
   <si>
-    <t xml:space="preserve">pearl lab </t>
+    <t xml:space="preserve">Lab Vendor 4</t>
   </si>
   <si>
-    <t>Oral Design</t>
+    <t>Lab Vendor 5</t>
   </si>
   <si>
-    <t>Sahara Lab</t>
+    <t>Lab Vendor 6</t>
   </si>
   <si>
-    <t>Italian Lab</t>
+    <t>Lab Vendor 7</t>
   </si>
   <si>
-    <t>Diamond Lab</t>
+    <t>Lab Vendor 8</t>
   </si>
   <si>
     <t>Dr. Lab cost</t>
   </si>
   <si>
-    <t>Dr.Anas</t>
+    <t>Doctor A</t>
   </si>
   <si>
     <t>Dr.Riyadh</t>
   </si>
   <si>
-    <t>Dr.Irina</t>
+    <t>Doctor B</t>
   </si>
   <si>
-    <t>Dr.WAEL</t>
+    <t>Doctor C</t>
   </si>
   <si>
     <t>Column5</t>
@@ -281,7 +281,7 @@
     <t>night guard lower</t>
   </si>
   <si>
-    <t>ZIRCON POST oLESYA nf6344(ASK PRICE)</t>
+    <t>SAMPLE TREATMENT NOTE</t>
   </si>
   <si>
     <t>NET TOTAL</t>
@@ -312,14 +312,14 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t xml:space="preserve"> Wael </t>
+      <t xml:space="preserve"> Doctor C </t>
     </r>
   </si>
   <si>
     <t>2021-May</t>
   </si>
   <si>
-    <t>Dr Wael (Surg)</t>
+    <t>Doctor C (Surg)</t>
   </si>
   <si>
     <t>Date</t>
@@ -474,13 +474,13 @@
     <t>OPG</t>
   </si>
   <si>
-    <t>Gulira 25-71</t>
+    <t>Patient A</t>
   </si>
   <si>
-    <t>Savita</t>
+    <t>Patient B</t>
   </si>
   <si>
-    <t>Rabel NF6147</t>
+    <t>Patient C</t>
   </si>
 </sst>
 </file>
@@ -1093,10 +1093,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="N2:T13" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="7">
     <tableColumn name="Dr. Lab cost" id="1"/>
-    <tableColumn name="Dr.Anas" id="2"/>
+    <tableColumn name="Doctor A" id="2"/>
     <tableColumn name="Dr.Riyadh" id="3"/>
-    <tableColumn name="Dr.Irina" id="4"/>
-    <tableColumn name="Dr.WAEL" id="5"/>
+    <tableColumn name="Doctor B" id="4"/>
+    <tableColumn name="Doctor C" id="5"/>
     <tableColumn name="Column5" id="6"/>
     <tableColumn name="Column6" id="7"/>
   </tableColumns>
